--- a/Analysed/GPT_gpt-5.4-2026-03-05_naive.xlsx
+++ b/Analysed/GPT_gpt-5.4-2026-03-05_naive.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H2" t="n">
-        <v>5.021728395061729</v>
+        <v>5.021446153846154</v>
       </c>
       <c r="I2" t="n">
-        <v>5.021742233700212</v>
+        <v>5.021462520636179</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9504643962848297</v>
+        <v>0.9475308641975309</v>
       </c>
     </row>
     <row r="3">
@@ -693,10 +693,10 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>7.186800000000001</v>
+        <v>7.188199999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>7.276078889072053</v>
+        <v>7.277808049131277</v>
       </c>
       <c r="J6" t="n">
         <v>0.3265306122448979</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009520958083832336</v>
+        <v>0.009552238805970149</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01102528395224109</v>
+        <v>0.01106291370758592</v>
       </c>
       <c r="J8" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9730538922155688</v>
       </c>
     </row>
     <row r="9">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H9" t="n">
-        <v>5.0168156424581</v>
+        <v>5.016833333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>5.016828050387101</v>
+        <v>5.016845677869268</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9438202247191011</v>
+        <v>0.9385474860335196</v>
       </c>
     </row>
     <row r="10">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6754237288135593</v>
+        <v>0.6808333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7590571761140062</v>
+        <v>0.7636960564692387</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4310344827586207</v>
+        <v>0.4406779661016949</v>
       </c>
     </row>
     <row r="13">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8135483870967742</v>
+        <v>0.8114400000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1.000166921552469</v>
+        <v>0.9973721471948174</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2357723577235772</v>
+        <v>0.2419354838709677</v>
       </c>
     </row>
     <row r="27">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>2.572463768115944</v>
+        <v>2.610000000000002</v>
       </c>
       <c r="I33" t="n">
-        <v>3.141341908405907</v>
+        <v>3.180148244523025</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>1.566666666666669</v>
+        <v>2.776666666666668</v>
       </c>
       <c r="I37" t="n">
-        <v>2.591653268990023</v>
+        <v>3.756283624364203</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7</v>
+        <v>0.7931034482758621</v>
       </c>
     </row>
     <row r="38">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
-        <v>4.386956521739131</v>
+        <v>4.36</v>
       </c>
       <c r="I42" t="n">
-        <v>4.908758808851608</v>
+        <v>4.848240918106276</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6530612244897959</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43" t="n">
-        <v>1.438333333333333</v>
+        <v>1.481428571428571</v>
       </c>
       <c r="I43" t="n">
-        <v>1.889108255235787</v>
+        <v>1.872598652751228</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H44" t="n">
-        <v>4.915644171779141</v>
+        <v>5.046969696969697</v>
       </c>
       <c r="I44" t="n">
-        <v>6.417947228340762</v>
+        <v>6.610417673504588</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2584615384615385</v>
+        <v>0.2613981762917933</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="H45" t="n">
-        <v>4.248275862068966</v>
+        <v>4.59809756097561</v>
       </c>
       <c r="I45" t="n">
-        <v>5.514549251595806</v>
+        <v>5.679381836853416</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3826086956521739</v>
+        <v>0.3137254901960784</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="H46" t="n">
-        <v>4.812666666666667</v>
+        <v>4.248275862068966</v>
       </c>
       <c r="I46" t="n">
-        <v>5.961053598148569</v>
+        <v>5.514549251595806</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.3826086956521739</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="H47" t="n">
-        <v>5.335454545454548</v>
+        <v>4.812666666666667</v>
       </c>
       <c r="I47" t="n">
-        <v>6.500136082491589</v>
+        <v>5.961053598148569</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3483146067415731</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H48" t="n">
-        <v>2.886585365853658</v>
+        <v>5.335454545454548</v>
       </c>
       <c r="I48" t="n">
-        <v>3.473643971253298</v>
+        <v>6.500136082491589</v>
       </c>
       <c r="J48" t="n">
-        <v>0.45</v>
+        <v>0.2962962962962963</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="H49" t="n">
-        <v>1.452222222222222</v>
+        <v>2.886585365853658</v>
       </c>
       <c r="I49" t="n">
-        <v>1.784304141630924</v>
+        <v>3.473643971253298</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8248407643312102</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="H50" t="n">
-        <v>1.835948717948718</v>
+        <v>1.452222222222222</v>
       </c>
       <c r="I50" t="n">
-        <v>2.239566922420494</v>
+        <v>1.784304141630924</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.8248407643312102</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>1.417477477477477</v>
+        <v>1.88005</v>
       </c>
       <c r="I51" t="n">
-        <v>1.686325500516936</v>
+        <v>2.283696236367701</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9095477386934674</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="H52" t="n">
-        <v>1.81825</v>
+        <v>1.417477477477477</v>
       </c>
       <c r="I52" t="n">
-        <v>2.226350713611852</v>
+        <v>1.686325500516936</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7721518987341772</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="53">
@@ -2754,20 +2754,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H53" t="n">
-        <v>3.13265306122449</v>
+        <v>1.81825</v>
       </c>
       <c r="I53" t="n">
-        <v>3.585182089133675</v>
+        <v>2.226350713611852</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.7721518987341772</v>
       </c>
     </row>
     <row r="54">
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3.549149193820964</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6326530612244898</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gpt-5.4-2026-03-05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>30</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>4.554666666666666</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>5.465163004583364</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.5862068965517241</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.3929</v>
+        <v>2.4593</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7519</v>
+        <v>1.7594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.3929 ± 1.7519</t>
+          <t>2.4593 ± 1.7594</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7905</v>
+        <v>2.8686</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8978</v>
+        <v>1.9296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.7905 ± 1.8978</t>
+          <t>2.8686 ± 1.9296</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6181</v>
+        <v>0.6113</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2482</v>
+        <v>0.2489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6181 ± 0.2482</t>
+          <t>0.6113 ± 0.2489</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0424</v>
+        <v>4.0426</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3305</v>
+        <v>2.3309</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1603</v>
+        <v>4.1606</v>
       </c>
       <c r="G2" t="n">
-        <v>0.727</v>
+        <v>0.7266</v>
       </c>
       <c r="H2" t="n">
-        <v>126.5</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="3">
@@ -3035,19 +3079,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6822</v>
+        <v>1.6831</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3435</v>
+        <v>2.343</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9733</v>
+        <v>1.9741</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7362</v>
+        <v>0.737</v>
       </c>
       <c r="H4" t="n">
-        <v>135.2</v>
+        <v>135.7</v>
       </c>
     </row>
     <row r="5">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1441</v>
+        <v>2.352</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4332</v>
+        <v>0.3907</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7615</v>
+        <v>2.962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4658</v>
+        <v>0.4831</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2747</v>
+        <v>1.2743</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4165</v>
+        <v>0.417</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5767</v>
+        <v>1.5762</v>
       </c>
       <c r="G7" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="H7" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1072</v>
+        <v>2.1098</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2451</v>
+        <v>1.2292</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5009</v>
+        <v>2.488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7546</v>
       </c>
       <c r="H8" t="n">
-        <v>129.3</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3685</v>
+        <v>2.3654</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3018</v>
+        <v>1.2901</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8311</v>
+        <v>2.8325</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7634</v>
+        <v>0.7573</v>
       </c>
       <c r="H9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4397</v>
+        <v>4.488</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1807</v>
+        <v>0.9113</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5735</v>
+        <v>5.6232</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3471</v>
+        <v>0.3421</v>
       </c>
       <c r="H10" t="n">
-        <v>125.6</v>
+        <v>139.5</v>
       </c>
     </row>
   </sheetData>
